--- a/config/devPOD.xlsx
+++ b/config/devPOD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F69D7442-2CCD-4DA4-97AD-9254FCB7A267}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D6E3CC8-FF91-4CEA-ACB6-DDB2772F7D44}"/>
   <bookViews>
-    <workbookView xWindow="-18120" yWindow="-2550" windowWidth="18240" windowHeight="28440" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -1943,7 +1943,7 @@
         <v>49</v>
       </c>
       <c r="F4" s="11">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G4" s="29" t="s">
         <v>21</v>

--- a/config/devPOD.xlsx
+++ b/config/devPOD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D6E3CC8-FF91-4CEA-ACB6-DDB2772F7D44}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14511BDD-8D66-4290-8F4C-96CCFF462248}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
@@ -3072,7 +3072,7 @@
         <v>48</v>
       </c>
       <c r="F18" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>16</v>
